--- a/data/trans_orig/IP18E-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP18E-Clase-trans_orig.xlsx
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3726</t>
+          <t>3898</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3786</t>
+          <t>4215</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,38%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2148</t>
+          <t>2151</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9579</t>
+          <t>9327</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1289</t>
+          <t>1799</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7495</t>
+          <t>7648</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>4536</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>13927</t>
+          <t>14724</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>8,31%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3754</t>
+          <t>4243</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>12101</t>
+          <t>12790</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>7149</t>
+          <t>6677</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>16945</t>
+          <t>17274</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>20,74%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>12914</t>
+          <t>13370</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>25772</t>
+          <t>25804</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>14,57%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>75118</t>
+          <t>75420</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>85772</t>
+          <t>85828</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>80,07%</t>
+          <t>80,39%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>91,43%</t>
+          <t>91,49%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>61625</t>
+          <t>61394</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>72460</t>
+          <t>72786</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>73,98%</t>
+          <t>73,71%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>86,99%</t>
+          <t>87,38%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>141016</t>
+          <t>140943</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>156603</t>
+          <t>156485</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>79,62%</t>
+          <t>79,58%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>88,42%</t>
+          <t>88,36%</t>
         </is>
       </c>
     </row>
@@ -1307,7 +1307,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3479</t>
+          <t>3368</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1377,7 +1377,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4132</t>
+          <t>3925</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,59%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1915</t>
+          <t>1936</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8573</t>
+          <t>8703</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1271</t>
+          <t>1317</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6739</t>
+          <t>6882</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4441</t>
+          <t>4553</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>13416</t>
+          <t>13304</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,78%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1304</t>
+          <t>1316</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7255</t>
+          <t>7439</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1120</t>
+          <t>645</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>6574</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>3130</t>
+          <t>3145</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>11054</t>
+          <t>11389</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,51%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>64917</t>
+          <t>65767</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>73916</t>
+          <t>74364</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>82,19%</t>
+          <t>83,27%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>93,58%</t>
+          <t>94,15%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>62183</t>
+          <t>61890</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>69842</t>
+          <t>69370</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>85,65%</t>
+          <t>85,25%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>95,55%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>130685</t>
+          <t>130254</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>141815</t>
+          <t>141508</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>86,21%</t>
+          <t>85,93%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>93,56%</t>
+          <t>93,35%</t>
         </is>
       </c>
     </row>
@@ -1984,12 +1984,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>537</t>
+          <t>542</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5979</t>
+          <t>6311</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1999,12 +1999,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2038</t>
+          <t>2088</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>8982</t>
+          <t>8779</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2034,12 +2034,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2054,12 +2054,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>3147</t>
+          <t>3172</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>11711</t>
+          <t>11365</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>7,88%</t>
         </is>
       </c>
     </row>
@@ -2137,7 +2137,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3065</t>
+          <t>3269</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,7 +2172,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3316</t>
+          <t>3488</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,7 +2187,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,42%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>53393</t>
+          <t>53061</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>58835</t>
+          <t>58830</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,93%</t>
+          <t>89,37%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>75136</t>
+          <t>75045</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>82550</t>
+          <t>82532</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>88,58%</t>
+          <t>88,47%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,3%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>131062</t>
+          <t>131700</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>140491</t>
+          <t>140503</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,89%</t>
+          <t>91,33%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,44%</t>
         </is>
       </c>
     </row>
@@ -2553,12 +2553,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2182</t>
+          <t>2287</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>8985</t>
+          <t>9145</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,12 +2568,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,12 +2588,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1483</t>
+          <t>1476</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>8260</t>
+          <t>8671</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2608,7 +2608,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,12 +2623,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>5117</t>
+          <t>5011</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>14883</t>
+          <t>14472</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,12 +2638,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,23%</t>
         </is>
       </c>
     </row>
@@ -2666,12 +2666,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1957</t>
+          <t>1818</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>9161</t>
+          <t>8665</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2681,12 +2681,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2701,12 +2701,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1161</t>
+          <t>1154</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>7531</t>
+          <t>7039</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2716,12 +2716,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>4280</t>
+          <t>4439</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>12718</t>
+          <t>13102</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2751,12 +2751,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,83%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>152889</t>
+          <t>152770</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>162652</t>
+          <t>162324</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>90,99%</t>
+          <t>90,92%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>160973</t>
+          <t>161258</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>169931</t>
+          <t>169907</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>92,52%</t>
+          <t>92,69%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>318102</t>
+          <t>317658</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>330742</t>
+          <t>330692</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>93,01%</t>
+          <t>92,88%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,69%</t>
         </is>
       </c>
     </row>
@@ -3127,7 +3127,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>3703</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>5365</t>
+          <t>5105</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3177,7 +3177,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3192,12 +3192,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>790</t>
+          <t>689</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>6470</t>
+          <t>6521</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3207,12 +3207,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,48%</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>82177</t>
+          <t>82135</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -3363,7 +3363,7 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,69%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
@@ -3383,7 +3383,7 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>96078</t>
+          <t>96338</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>94,97%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>180812</t>
+          <t>180761</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>186492</t>
+          <t>186593</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3433,12 +3433,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,63%</t>
         </is>
       </c>
     </row>
@@ -3696,7 +3696,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>4617</t>
+          <t>4858</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3711,7 +3711,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3731,7 +3731,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>4925</t>
+          <t>4799</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3746,7 +3746,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>688</t>
+          <t>791</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7108</t>
+          <t>6745</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3776,12 +3776,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,01%</t>
         </is>
       </c>
     </row>
@@ -3804,12 +3804,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>659</t>
+          <t>664</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>5569</t>
+          <t>5609</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3824,7 +3824,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>671</t>
+          <t>665</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>6668</t>
+          <t>6134</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3854,12 +3854,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1980</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>8862</t>
+          <t>9488</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3889,12 +3889,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>7,05%</t>
         </is>
       </c>
     </row>
@@ -3917,12 +3917,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>61348</t>
+          <t>60765</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>66984</t>
+          <t>66895</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3932,12 +3932,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>89,99%</t>
+          <t>89,14%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,13%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3952,12 +3952,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>57902</t>
+          <t>58115</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>64929</t>
+          <t>64838</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3967,12 +3967,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>87,23%</t>
+          <t>87,55%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>121570</t>
+          <t>121747</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>131034</t>
+          <t>130576</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4002,12 +4002,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>90,35%</t>
+          <t>90,49%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,05%</t>
         </is>
       </c>
     </row>
@@ -4152,7 +4152,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>3439</t>
+          <t>3423</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4187,7 +4187,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>3438</t>
+          <t>3911</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4202,7 +4202,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4222,7 +4222,7 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>4111</t>
+          <t>4796</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4237,7 +4237,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,42%</t>
         </is>
       </c>
     </row>
@@ -4260,12 +4260,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>12699</t>
+          <t>13164</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>27110</t>
+          <t>26713</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4275,12 +4275,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4295,12 +4295,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>12393</t>
+          <t>12602</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>26337</t>
+          <t>26584</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4310,12 +4310,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4330,12 +4330,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>28222</t>
+          <t>28909</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>47711</t>
+          <t>48075</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4345,12 +4345,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,23%</t>
         </is>
       </c>
     </row>
@@ -4373,12 +4373,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>12053</t>
+          <t>11588</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>26077</t>
+          <t>24482</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4388,12 +4388,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4408,12 +4408,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>14500</t>
+          <t>14518</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>29191</t>
+          <t>28801</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4428,7 +4428,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>28840</t>
+          <t>29874</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>49016</t>
+          <t>49070</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,32%</t>
         </is>
       </c>
     </row>
@@ -4486,12 +4486,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>506003</t>
+          <t>506830</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>525139</t>
+          <t>525397</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4501,12 +4501,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>91,3%</t>
+          <t>91,45%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>94,76%</t>
+          <t>94,8%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4521,12 +4521,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>531562</t>
+          <t>531108</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>551516</t>
+          <t>550620</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4536,12 +4536,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>91,25%</t>
+          <t>91,17%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>94,68%</t>
+          <t>94,52%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>1045354</t>
+          <t>1044540</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>1072251</t>
+          <t>1071758</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4571,12 +4571,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>91,96%</t>
+          <t>91,89%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>94,29%</t>
         </is>
       </c>
     </row>
@@ -5068,7 +5068,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2678</t>
+          <t>3557</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5083,7 +5083,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5103,7 +5103,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5333</t>
+          <t>4616</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5118,7 +5118,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>604</t>
+          <t>606</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>5379</t>
+          <t>5255</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5153,7 +5153,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,11%</t>
         </is>
       </c>
     </row>
@@ -5176,12 +5176,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4422</t>
+          <t>4309</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>13081</t>
+          <t>13606</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5191,12 +5191,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5928</t>
+          <t>5958</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>15587</t>
+          <t>16228</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5226,12 +5226,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>18,76%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>12178</t>
+          <t>12315</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>25249</t>
+          <t>25866</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5261,12 +5261,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>15,29%</t>
         </is>
       </c>
     </row>
@@ -5289,12 +5289,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>68619</t>
+          <t>68742</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>77731</t>
+          <t>77893</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>83,08%</t>
+          <t>83,23%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>94,31%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5324,12 +5324,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>69066</t>
+          <t>68205</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>79355</t>
+          <t>79301</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5339,12 +5339,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>79,82%</t>
+          <t>78,82%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>91,71%</t>
+          <t>91,65%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5359,12 +5359,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>141678</t>
+          <t>141193</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>155375</t>
+          <t>155162</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5374,12 +5374,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>83,77%</t>
+          <t>83,49%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>91,87%</t>
+          <t>91,75%</t>
         </is>
       </c>
     </row>
@@ -5524,7 +5524,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3332</t>
+          <t>3263</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5539,7 +5539,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5594,7 +5594,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>3283</t>
+          <t>3314</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5609,7 +5609,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,87%</t>
         </is>
       </c>
     </row>
@@ -5632,12 +5632,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1401</t>
+          <t>1397</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8148</t>
+          <t>7943</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5652,7 +5652,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5667,12 +5667,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>826</t>
+          <t>1199</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7662</t>
+          <t>8533</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5682,12 +5682,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5702,12 +5702,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3414</t>
+          <t>3169</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>12208</t>
+          <t>12141</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5717,12 +5717,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,86%</t>
         </is>
       </c>
     </row>
@@ -5745,12 +5745,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4070</t>
+          <t>3829</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>12696</t>
+          <t>12630</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5760,12 +5760,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5780,12 +5780,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1989</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>8971</t>
+          <t>8945</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5795,12 +5795,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5815,12 +5815,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>7544</t>
+          <t>7543</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>18529</t>
+          <t>18282</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5835,7 +5835,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,33%</t>
         </is>
       </c>
     </row>
@@ -5858,12 +5858,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>70616</t>
+          <t>69917</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>80964</t>
+          <t>80979</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5873,12 +5873,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>79,82%</t>
+          <t>79,03%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>91,52%</t>
+          <t>91,53%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5893,12 +5893,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>75218</t>
+          <t>74871</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>84221</t>
+          <t>84100</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5908,12 +5908,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>85,03%</t>
+          <t>84,64%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>95,07%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5928,12 +5928,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>149720</t>
+          <t>149518</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>163898</t>
+          <t>163640</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5943,12 +5943,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>84,62%</t>
+          <t>84,51%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>92,64%</t>
+          <t>92,49%</t>
         </is>
       </c>
     </row>
@@ -6093,7 +6093,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4585</t>
+          <t>4609</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6108,7 +6108,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6163,7 +6163,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4635</t>
+          <t>4634</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6206,7 +6206,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3933</t>
+          <t>4502</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6221,7 +6221,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -6241,7 +6241,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3410</t>
+          <t>3401</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6256,7 +6256,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -6271,12 +6271,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>638</t>
+          <t>634</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>5296</t>
+          <t>5249</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -6291,7 +6291,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,16%</t>
         </is>
       </c>
     </row>
@@ -6319,7 +6319,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3088</t>
+          <t>3604</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6334,7 +6334,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6354,7 +6354,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5180</t>
+          <t>5173</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6369,7 +6369,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6384,12 +6384,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>680</t>
+          <t>678</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5799</t>
+          <t>6381</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6404,7 +6404,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,84%</t>
         </is>
       </c>
     </row>
@@ -6427,12 +6427,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>75423</t>
+          <t>75099</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>81683</t>
+          <t>81454</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6442,12 +6442,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,57%</t>
+          <t>91,18%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>98,89%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6462,12 +6462,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>77164</t>
+          <t>77816</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>82941</t>
+          <t>82942</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6477,7 +6477,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,29%</t>
+          <t>93,07%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -6497,12 +6497,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>156580</t>
+          <t>156484</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>163920</t>
+          <t>163962</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6512,12 +6512,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,34%</t>
+          <t>94,28%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,78%</t>
         </is>
       </c>
     </row>
@@ -6770,12 +6770,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1976</t>
+          <t>2125</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>9631</t>
+          <t>9721</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6785,12 +6785,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6805,12 +6805,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1342</t>
+          <t>1327</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>7973</t>
+          <t>8165</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6820,12 +6820,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6840,12 +6840,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>4994</t>
+          <t>4685</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>14984</t>
+          <t>14024</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6855,12 +6855,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,46%</t>
         </is>
       </c>
     </row>
@@ -6883,12 +6883,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>754</t>
+          <t>683</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>7200</t>
+          <t>7055</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6898,12 +6898,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6918,12 +6918,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>3676</t>
+          <t>3791</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>13524</t>
+          <t>13108</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6933,12 +6933,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6953,12 +6953,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>6061</t>
+          <t>5883</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>17150</t>
+          <t>16965</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6968,12 +6968,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,18%</t>
         </is>
       </c>
     </row>
@@ -6996,12 +6996,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>178484</t>
+          <t>177646</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>187382</t>
+          <t>187492</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7011,12 +7011,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>93,25%</t>
+          <t>92,81%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,96%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7031,12 +7031,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>196894</t>
+          <t>196606</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>207864</t>
+          <t>207654</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7046,12 +7046,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>91,81%</t>
+          <t>91,68%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7066,12 +7066,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>378274</t>
+          <t>379519</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>392723</t>
+          <t>393541</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7081,12 +7081,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>93,21%</t>
+          <t>93,51%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,97%</t>
         </is>
       </c>
     </row>
@@ -7344,7 +7344,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4651</t>
+          <t>5522</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7359,7 +7359,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7379,7 +7379,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>5004</t>
+          <t>4142</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7394,7 +7394,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7409,12 +7409,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>620</t>
+          <t>624</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>6216</t>
+          <t>6125</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7429,7 +7429,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,26%</t>
         </is>
       </c>
     </row>
@@ -7457,7 +7457,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3292</t>
+          <t>3240</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7472,7 +7472,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7527,7 +7527,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3229</t>
+          <t>3233</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7565,7 +7565,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>132040</t>
+          <t>131764</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -7580,7 +7580,7 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>95,72%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
@@ -7600,7 +7600,7 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>128810</t>
+          <t>129672</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
@@ -7615,7 +7615,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -7635,12 +7635,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>264490</t>
+          <t>264257</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>270779</t>
+          <t>270554</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -7650,12 +7650,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>99,75%</t>
+          <t>99,66%</t>
         </is>
       </c>
     </row>
@@ -7913,7 +7913,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>5290</t>
+          <t>5530</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7928,7 +7928,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7948,7 +7948,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>2306</t>
+          <t>2314</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7963,7 +7963,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7978,12 +7978,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>622</t>
+          <t>696</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>5833</t>
+          <t>6185</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7993,12 +7993,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>5,07%</t>
         </is>
       </c>
     </row>
@@ -8061,7 +8061,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>3139</t>
+          <t>3605</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -8076,7 +8076,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -8096,7 +8096,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>3534</t>
+          <t>2550</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -8111,7 +8111,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,09%</t>
         </is>
       </c>
     </row>
@@ -8134,7 +8134,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>47370</t>
+          <t>47130</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -8149,7 +8149,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>89,95%</t>
+          <t>89,5%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -8169,7 +8169,7 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>65494</t>
+          <t>65782</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
@@ -8184,7 +8184,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>94,4%</t>
+          <t>94,82%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -8204,12 +8204,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>115477</t>
+          <t>115271</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>121354</t>
+          <t>120907</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -8219,12 +8219,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>94,62%</t>
+          <t>94,45%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,07%</t>
         </is>
       </c>
     </row>
@@ -8369,7 +8369,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>5633</t>
+          <t>5563</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8384,7 +8384,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8439,7 +8439,7 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>5234</t>
+          <t>6061</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8454,7 +8454,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,46%</t>
         </is>
       </c>
     </row>
@@ -8477,12 +8477,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>8295</t>
+          <t>8054</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>20397</t>
+          <t>21427</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -8492,12 +8492,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>6172</t>
+          <t>5568</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>16570</t>
+          <t>15925</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -8527,12 +8527,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -8547,12 +8547,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>17080</t>
+          <t>17444</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>32540</t>
+          <t>34425</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -8562,12 +8562,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,63%</t>
         </is>
       </c>
     </row>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>13405</t>
+          <t>12777</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>27488</t>
+          <t>27405</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -8605,12 +8605,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -8625,12 +8625,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>17677</t>
+          <t>16952</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>33714</t>
+          <t>33111</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -8640,12 +8640,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -8660,12 +8660,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>34324</t>
+          <t>33645</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>54832</t>
+          <t>56045</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -8675,12 +8675,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,27%</t>
         </is>
       </c>
     </row>
@@ -8703,12 +8703,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>590812</t>
+          <t>590417</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>608761</t>
+          <t>609532</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -8718,12 +8718,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>93,02%</t>
+          <t>92,96%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -8738,12 +8738,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>630764</t>
+          <t>630265</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>650389</t>
+          <t>649893</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -8753,12 +8753,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>93,2%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -8773,12 +8773,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>1227346</t>
+          <t>1227208</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>1254932</t>
+          <t>1254761</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -8788,12 +8788,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>93,59%</t>
+          <t>93,58%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>95,68%</t>
         </is>
       </c>
     </row>
@@ -9285,7 +9285,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4599</t>
+          <t>4484</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9300,7 +9300,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9315,12 +9315,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>631</t>
+          <t>638</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5608</t>
+          <t>6757</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9330,12 +9330,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9350,12 +9350,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1185</t>
+          <t>1238</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>7498</t>
+          <t>7679</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9365,12 +9365,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,56%</t>
         </is>
       </c>
     </row>
@@ -9393,12 +9393,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4170</t>
+          <t>3651</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>13186</t>
+          <t>11952</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9408,12 +9408,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>15,57%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9428,12 +9428,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>6678</t>
+          <t>6944</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>16897</t>
+          <t>16824</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9443,12 +9443,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>18,47%</t>
+          <t>18,39%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9463,12 +9463,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>12536</t>
+          <t>13009</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>25382</t>
+          <t>26239</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -9478,12 +9478,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>15,6%</t>
         </is>
       </c>
     </row>
@@ -9506,12 +9506,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>62075</t>
+          <t>63154</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>71731</t>
+          <t>72195</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -9521,12 +9521,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>80,89%</t>
+          <t>82,29%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>93,47%</t>
+          <t>94,07%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9541,12 +9541,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>72271</t>
+          <t>72036</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>83523</t>
+          <t>82952</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9556,12 +9556,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>78,99%</t>
+          <t>78,73%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>91,29%</t>
+          <t>90,66%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9576,12 +9576,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>139190</t>
+          <t>138431</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>153242</t>
+          <t>152280</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9591,12 +9591,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>82,73%</t>
+          <t>82,28%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>91,09%</t>
+          <t>90,52%</t>
         </is>
       </c>
     </row>
@@ -9849,12 +9849,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>618</t>
+          <t>722</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6419</t>
+          <t>6505</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9864,12 +9864,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9884,12 +9884,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>639</t>
+          <t>638</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5705</t>
+          <t>6153</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9904,7 +9904,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9919,12 +9919,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2095</t>
+          <t>2088</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8989</t>
+          <t>9709</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9934,12 +9934,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,98%</t>
         </is>
       </c>
     </row>
@@ -9962,12 +9962,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6354</t>
+          <t>6300</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>15895</t>
+          <t>16153</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9977,12 +9977,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9997,12 +9997,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5305</t>
+          <t>5006</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>14735</t>
+          <t>15159</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10012,12 +10012,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10032,12 +10032,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>13376</t>
+          <t>13850</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>27229</t>
+          <t>27588</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10047,12 +10047,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>14,16%</t>
         </is>
       </c>
     </row>
@@ -10075,12 +10075,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>77780</t>
+          <t>77516</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>88510</t>
+          <t>88400</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10090,12 +10090,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>80,24%</t>
+          <t>79,97%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>91,31%</t>
+          <t>91,2%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10110,12 +10110,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>80880</t>
+          <t>80508</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>90802</t>
+          <t>90821</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10125,12 +10125,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>82,57%</t>
+          <t>82,2%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>92,71%</t>
+          <t>92,72%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10145,12 +10145,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>162327</t>
+          <t>162289</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>176353</t>
+          <t>177372</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10160,12 +10160,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>83,3%</t>
+          <t>83,28%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>90,49%</t>
+          <t>91,02%</t>
         </is>
       </c>
     </row>
@@ -10423,7 +10423,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3256</t>
+          <t>3416</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10438,7 +10438,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -10458,7 +10458,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3725</t>
+          <t>3686</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10473,7 +10473,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -10488,12 +10488,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>511</t>
+          <t>510</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>4902</t>
+          <t>4935</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10508,7 +10508,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,05%</t>
         </is>
       </c>
     </row>
@@ -10531,12 +10531,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>583</t>
+          <t>590</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5931</t>
+          <t>5520</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10546,12 +10546,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10566,12 +10566,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1416</t>
+          <t>1748</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7559</t>
+          <t>7798</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10581,12 +10581,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10601,12 +10601,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2785</t>
+          <t>3060</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>10692</t>
+          <t>10950</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10616,12 +10616,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,99%</t>
         </is>
       </c>
     </row>
@@ -10644,12 +10644,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>48012</t>
+          <t>48343</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>53620</t>
+          <t>53645</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10659,12 +10659,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>87,65%</t>
+          <t>88,25%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10679,12 +10679,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>57810</t>
+          <t>57801</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>64654</t>
+          <t>64561</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10694,12 +10694,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>86,2%</t>
+          <t>86,18%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10714,12 +10714,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>108683</t>
+          <t>108223</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>117545</t>
+          <t>117208</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10729,12 +10729,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>89,2%</t>
+          <t>88,82%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,19%</t>
         </is>
       </c>
     </row>
@@ -10987,12 +10987,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1350</t>
+          <t>1266</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>7637</t>
+          <t>7644</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11002,12 +11002,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11027,7 +11027,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>2920</t>
+          <t>3228</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11042,7 +11042,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11057,12 +11057,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1765</t>
+          <t>1830</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>8533</t>
+          <t>7924</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11072,12 +11072,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,0%</t>
         </is>
       </c>
     </row>
@@ -11100,12 +11100,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2699</t>
+          <t>3064</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>11078</t>
+          <t>10358</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -11135,12 +11135,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1497</t>
+          <t>1799</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>8548</t>
+          <t>8830</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11150,12 +11150,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -11170,12 +11170,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>5355</t>
+          <t>5674</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>16341</t>
+          <t>16165</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11185,12 +11185,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,08%</t>
         </is>
       </c>
     </row>
@@ -11213,12 +11213,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>192473</t>
+          <t>192142</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>202041</t>
+          <t>201641</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>92,86%</t>
+          <t>92,7%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11248,12 +11248,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>179535</t>
+          <t>179315</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>187051</t>
+          <t>187022</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11263,12 +11263,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>94,87%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11283,12 +11283,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>374917</t>
+          <t>374987</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>387642</t>
+          <t>387331</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11298,12 +11298,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>94,62%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,74%</t>
         </is>
       </c>
     </row>
@@ -11561,7 +11561,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3669</t>
+          <t>2749</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -11576,7 +11576,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -11596,7 +11596,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>5763</t>
+          <t>5089</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -11611,7 +11611,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -11626,12 +11626,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>606</t>
+          <t>605</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>5790</t>
+          <t>5401</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -11646,7 +11646,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,13%</t>
         </is>
       </c>
     </row>
@@ -11674,7 +11674,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3066</t>
+          <t>3867</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -11689,7 +11689,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -11709,7 +11709,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2872</t>
+          <t>2774</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -11724,7 +11724,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -11744,7 +11744,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4253</t>
+          <t>4792</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -11759,7 +11759,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,89%</t>
         </is>
       </c>
     </row>
@@ -11782,7 +11782,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>120228</t>
+          <t>120006</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -11797,7 +11797,7 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
@@ -11817,7 +11817,7 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>123046</t>
+          <t>123079</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
@@ -11832,7 +11832,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,41%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -11852,12 +11852,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>245365</t>
+          <t>245817</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>252032</t>
+          <t>252127</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -11867,12 +11867,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,57%</t>
         </is>
       </c>
     </row>
@@ -12130,7 +12130,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>4834</t>
+          <t>4818</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -12145,7 +12145,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -12200,7 +12200,7 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>4140</t>
+          <t>4855</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -12215,7 +12215,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>4,12%</t>
         </is>
       </c>
     </row>
@@ -12243,7 +12243,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>3473</t>
+          <t>4542</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -12258,7 +12258,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -12278,7 +12278,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>3880</t>
+          <t>4298</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -12293,7 +12293,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -12313,7 +12313,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>4753</t>
+          <t>5084</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -12328,7 +12328,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,31%</t>
         </is>
       </c>
     </row>
@@ -12351,12 +12351,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>50983</t>
+          <t>50651</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>55714</t>
+          <t>55718</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -12366,7 +12366,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>90,54%</t>
+          <t>89,95%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -12386,7 +12386,7 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>57725</t>
+          <t>57307</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
@@ -12401,7 +12401,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>93,7%</t>
+          <t>93,02%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -12421,12 +12421,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>111568</t>
+          <t>110957</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>117220</t>
+          <t>117151</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -12436,12 +12436,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>94,62%</t>
+          <t>94,1%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,35%</t>
         </is>
       </c>
     </row>
@@ -12694,12 +12694,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>5835</t>
+          <t>5879</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>16443</t>
+          <t>15879</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -12714,7 +12714,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -12729,12 +12729,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>3872</t>
+          <t>4266</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>12863</t>
+          <t>13513</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -12744,12 +12744,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -12764,12 +12764,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>12436</t>
+          <t>12129</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>26048</t>
+          <t>25665</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -12779,12 +12779,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,05%</t>
         </is>
       </c>
     </row>
@@ -12807,12 +12807,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>20745</t>
+          <t>19708</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>37239</t>
+          <t>36688</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -12822,12 +12822,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -12842,12 +12842,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>22061</t>
+          <t>21629</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>39006</t>
+          <t>38977</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -12857,7 +12857,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -12877,12 +12877,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>46336</t>
+          <t>45467</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>69062</t>
+          <t>69645</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -12892,12 +12892,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,56%</t>
         </is>
       </c>
     </row>
@@ -12920,12 +12920,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>567654</t>
+          <t>568665</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>586810</t>
+          <t>587059</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -12935,12 +12935,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>92,11%</t>
+          <t>92,28%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -12955,12 +12955,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>588474</t>
+          <t>588046</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>607319</t>
+          <t>607324</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -12970,7 +12970,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>92,51%</t>
+          <t>92,44%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -12990,12 +12990,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>1163134</t>
+          <t>1163832</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>1189979</t>
+          <t>1190497</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -13005,12 +13005,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>92,87%</t>
+          <t>92,93%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>95,06%</t>
         </is>
       </c>
     </row>
@@ -13497,12 +13497,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3487</t>
+          <t>3280</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13890</t>
+          <t>13847</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -13512,12 +13512,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>56,07%</t>
+          <t>55,9%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -13567,12 +13567,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>3362</t>
+          <t>3156</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>16189</t>
+          <t>16398</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -13582,12 +13582,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>35,73%</t>
+          <t>36,19%</t>
         </is>
       </c>
     </row>
@@ -13615,7 +13615,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4350</t>
+          <t>4245</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -13630,7 +13630,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -13650,7 +13650,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4561</t>
+          <t>4630</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -13665,7 +13665,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>22,54%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -13680,12 +13680,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>745</t>
+          <t>852</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>6330</t>
+          <t>6648</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -13695,12 +13695,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>14,67%</t>
         </is>
       </c>
     </row>
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9786</t>
+          <t>9522</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20148</t>
+          <t>20329</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -13738,12 +13738,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>39,5%</t>
+          <t>38,44%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>81,33%</t>
+          <t>82,06%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -13758,7 +13758,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>15977</t>
+          <t>15908</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -13773,7 +13773,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>77,79%</t>
+          <t>77,46%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -13793,12 +13793,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>27105</t>
+          <t>27444</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>39735</t>
+          <t>40068</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -13808,12 +13808,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>59,82%</t>
+          <t>60,57%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>87,69%</t>
+          <t>88,43%</t>
         </is>
       </c>
     </row>
@@ -14071,7 +14071,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4379</t>
+          <t>4408</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -14086,7 +14086,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>41,74%</t>
+          <t>42,02%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -14101,12 +14101,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>768</t>
+          <t>839</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6631</t>
+          <t>6595</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -14116,12 +14116,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>40,94%</t>
+          <t>40,72%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -14136,12 +14136,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1820</t>
+          <t>1786</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8550</t>
+          <t>8801</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -14151,12 +14151,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>32,04%</t>
+          <t>32,98%</t>
         </is>
       </c>
     </row>
@@ -14179,12 +14179,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1158</t>
+          <t>1230</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6106</t>
+          <t>6620</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -14194,12 +14194,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>58,2%</t>
+          <t>63,1%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -14249,12 +14249,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1071</t>
+          <t>1292</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>7006</t>
+          <t>7253</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -14264,12 +14264,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>26,25%</t>
+          <t>27,18%</t>
         </is>
       </c>
     </row>
@@ -14292,12 +14292,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2949</t>
+          <t>2762</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8377</t>
+          <t>8336</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -14307,12 +14307,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>28,11%</t>
+          <t>26,33%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>79,85%</t>
+          <t>79,46%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -14327,12 +14327,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>9565</t>
+          <t>9601</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>15428</t>
+          <t>15357</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -14342,12 +14342,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>59,06%</t>
+          <t>59,28%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>94,82%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -14362,12 +14362,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>14363</t>
+          <t>14712</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>22666</t>
+          <t>22327</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -14377,12 +14377,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>53,82%</t>
+          <t>55,13%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>84,93%</t>
+          <t>83,66%</t>
         </is>
       </c>
     </row>
@@ -14788,7 +14788,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3285</t>
+          <t>3851</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -14803,7 +14803,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>30,07%</t>
+          <t>35,24%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -14823,7 +14823,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3326</t>
+          <t>3379</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -14838,7 +14838,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>23,56%</t>
         </is>
       </c>
     </row>
@@ -14896,7 +14896,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>7641</t>
+          <t>7075</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -14911,7 +14911,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>69,93%</t>
+          <t>64,76%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -14931,7 +14931,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>11015</t>
+          <t>10962</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -14946,7 +14946,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>76,8%</t>
+          <t>76,44%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -15209,7 +15209,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4607</t>
+          <t>4168</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -15224,7 +15224,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -15244,7 +15244,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3215</t>
+          <t>3075</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -15259,7 +15259,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -15274,12 +15274,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>559</t>
+          <t>564</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>5132</t>
+          <t>4883</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -15289,12 +15289,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>6,85%</t>
         </is>
       </c>
     </row>
@@ -15352,12 +15352,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>418</t>
+          <t>440</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>5586</t>
+          <t>5367</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -15367,12 +15367,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -15387,12 +15387,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>417</t>
+          <t>428</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>5189</t>
+          <t>5788</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -15402,12 +15402,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>8,11%</t>
         </is>
       </c>
     </row>
@@ -15430,7 +15430,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>25595</t>
+          <t>26034</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -15445,7 +15445,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>84,75%</t>
+          <t>86,2%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -15465,12 +15465,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>35034</t>
+          <t>34912</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>40580</t>
+          <t>40508</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -15480,12 +15480,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>85,18%</t>
+          <t>84,88%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -15500,12 +15500,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>63421</t>
+          <t>62958</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>69853</t>
+          <t>69779</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -15515,12 +15515,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>88,91%</t>
+          <t>88,26%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>97,82%</t>
         </is>
       </c>
     </row>
@@ -15665,7 +15665,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1723</t>
+          <t>2574</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -15680,7 +15680,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -15735,7 +15735,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>2452</t>
+          <t>2226</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -15750,7 +15750,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,42%</t>
         </is>
       </c>
     </row>
@@ -15778,7 +15778,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2536</t>
+          <t>3188</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -15793,7 +15793,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -15848,7 +15848,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2581</t>
+          <t>2900</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -15863,7 +15863,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,76%</t>
         </is>
       </c>
     </row>
@@ -15999,7 +15999,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>17016</t>
+          <t>16882</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -16014,7 +16014,7 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>83,24%</t>
+          <t>82,59%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
@@ -16069,7 +16069,7 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>47122</t>
+          <t>46922</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
@@ -16084,7 +16084,7 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>93,6%</t>
+          <t>93,21%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
@@ -16347,7 +16347,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>2816</t>
+          <t>2968</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -16362,7 +16362,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>30,1%</t>
+          <t>31,73%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -16417,7 +16417,7 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>3375</t>
+          <t>3493</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -16432,7 +16432,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>16,61%</t>
         </is>
       </c>
     </row>
@@ -16495,7 +16495,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>3115</t>
+          <t>3910</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -16510,7 +16510,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>26,69%</t>
+          <t>33,5%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -16530,7 +16530,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>2706</t>
+          <t>3403</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -16545,7 +16545,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>16,18%</t>
         </is>
       </c>
     </row>
@@ -16568,7 +16568,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>6540</t>
+          <t>6388</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -16583,7 +16583,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>69,9%</t>
+          <t>68,27%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -16603,7 +16603,7 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>8556</t>
+          <t>7761</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
@@ -16618,7 +16618,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>73,31%</t>
+          <t>66,5%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -16638,7 +16638,7 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>16788</t>
+          <t>16648</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
@@ -16653,7 +16653,7 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>79,84%</t>
+          <t>79,17%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -16803,7 +16803,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>1761</t>
+          <t>2058</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -16818,7 +16818,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -16873,7 +16873,7 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>1993</t>
+          <t>1973</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -16888,7 +16888,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,86%</t>
         </is>
       </c>
     </row>
@@ -16911,12 +16911,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>6748</t>
+          <t>5760</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>21612</t>
+          <t>22063</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -16926,12 +16926,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>22,36%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -16946,12 +16946,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>1199</t>
+          <t>1204</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>8575</t>
+          <t>8852</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -16966,7 +16966,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -16981,12 +16981,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>8698</t>
+          <t>8635</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>25821</t>
+          <t>26989</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -16996,12 +16996,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,78%</t>
         </is>
       </c>
     </row>
@@ -17024,12 +17024,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>1790</t>
+          <t>1737</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>8707</t>
+          <t>8619</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -17039,12 +17039,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -17059,12 +17059,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>1864</t>
+          <t>1935</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>9192</t>
+          <t>9424</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -17074,12 +17074,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -17094,12 +17094,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>5255</t>
+          <t>4935</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>14608</t>
+          <t>14469</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -17109,12 +17109,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,32%</t>
         </is>
       </c>
     </row>
@@ -17137,12 +17137,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>72594</t>
+          <t>72694</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>87739</t>
+          <t>88567</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -17152,12 +17152,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>73,57%</t>
+          <t>73,67%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>88,91%</t>
+          <t>89,75%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -17172,12 +17172,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>116158</t>
+          <t>115547</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>126177</t>
+          <t>125836</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -17187,12 +17187,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>89,1%</t>
+          <t>88,64%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -17207,12 +17207,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>194508</t>
+          <t>192837</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>212288</t>
+          <t>212011</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -17222,12 +17222,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>84,92%</t>
+          <t>84,19%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>92,69%</t>
+          <t>92,56%</t>
         </is>
       </c>
     </row>
